--- a/results/job_matches_2026-06-13.xlsx
+++ b/results/job_matches_2026-06-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cybersecurity Data Engineer - AI/ML SME</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Kinesis, RDS, Spark, Scala, Kafka, Dask, ETL, MLOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9e656d2a85bee5</t>
+          <t>https://www.indeed.com/viewjob?jk=599be78bf8533a28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Experienced AWS Solutions Architect and Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kaizen Analytix LLC</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM, RDS</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f364a3ec32fde4</t>
+          <t>https://www.indeed.com/viewjob?jk=2b9e656d2a85bee5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Python / DevOps / Message Brokers</t>
+          <t>Experienced AWS Solutions Architect and Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Kaizen Analytix LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ccd83a736eef1f</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f364a3ec32fde4</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>AI/ML Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>QuidelOrtho Corporation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latham, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db4d87acabac99</t>
+          <t>https://www.indeed.com/viewjob?jk=83b31d482e2d3c8b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>QuidelOrtho Corporation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7edd80e431e58210</t>
+          <t>https://www.indeed.com/viewjob?jk=859e7ca77b35594f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Latham, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7af97ac7780e4ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=30db4d87acabac99</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6c83582ab47968</t>
+          <t>https://www.indeed.com/viewjob?jk=7edd80e431e58210</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06003d92ed7c2087</t>
+          <t>https://www.indeed.com/viewjob?jk=7af97ac7780e4ad6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AWS Infrastructure / Dev Ops Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Full Swing Golf Inc</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,29 +1221,29 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e2bb60d0f9bd54</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6c83582ab47968</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer/DevSecOps Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GetWellNetwork</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f8ca36b295c24d</t>
+          <t>https://www.indeed.com/viewjob?jk=06003d92ed7c2087</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AWS Full Stack Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hiring Group</t>
+          <t>Midrex Technologies Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc54c80bec441143</t>
+          <t>https://www.indeed.com/viewjob?jk=06f7fe854f6a6907</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AWS Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>uShip</t>
+          <t>Hiring Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae560083a24a530c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc54c80bec441143</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer, Platform Modernization (Data Warehouse Programmer/Analyst)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Caloptima</t>
+          <t>uShip</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dfe4169ae274aad</t>
+          <t>https://www.indeed.com/viewjob?jk=ae560083a24a530c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37aff8f440d6ba6d</t>
+          <t>https://www.indeed.com/viewjob?jk=6b4b729357fee0da</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer, Geospatial Data</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Civitech</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d28890cbb8b4f4</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5860ee0655d6fc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Scientific Games</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418149d6683bca23</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e67b07fb6f9c29</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Application Developer – Data &amp; Digital Solutions</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TC Energy</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b192109a8d9de9</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebd82ca33ca821</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure &amp; Microsoft Fabric</t>
+          <t>Data Engineer, Platform Modernization (Data Warehouse Programmer/Analyst)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Caloptima</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56fe4f99d705b6f4</t>
+          <t>https://www.indeed.com/viewjob?jk=0dfe4169ae274aad</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>K&amp;L GATES</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd2e06fdde37fe</t>
+          <t>https://www.indeed.com/viewjob?jk=37aff8f440d6ba6d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer, Geospatial Data</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Civitech</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adebbeb79bcc9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d28890cbb8b4f4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Scientific Games</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9760e71980916f</t>
+          <t>https://www.indeed.com/viewjob?jk=418149d6683bca23</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Application Developer – Data &amp; Digital Solutions</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>TC Energy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94cb48d5ed1c52af</t>
+          <t>https://www.indeed.com/viewjob?jk=87b192109a8d9de9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Migration Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbc89f3bdee8ad93</t>
+          <t>https://www.indeed.com/viewjob?jk=88c5b3637f5dab83</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer - Azure &amp; Microsoft Fabric</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c02b3eae0c4832e</t>
+          <t>https://www.indeed.com/viewjob?jk=56fe4f99d705b6f4</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da723ed84459a1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd2e06fdde37fe</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2dcb8f1f90f8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=adebbeb79bcc9a1c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Dimensional Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9760e71980916f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>iHeartMedia</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hive, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356a68911d5f594b</t>
+          <t>https://www.indeed.com/viewjob?jk=94cb48d5ed1c52af</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AWS Data Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df86eb0af63d38af</t>
+          <t>https://www.indeed.com/viewjob?jk=fbc89f3bdee8ad93</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d22bd46597ab543</t>
+          <t>https://www.indeed.com/viewjob?jk=4c02b3eae0c4832e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,42 +1991,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6f2596747788c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=da723ed84459a1ba</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer-1</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Flexential</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2dcb8f1f90f8bd</t>
         </is>
       </c>
     </row>
@@ -2048,20 +2048,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>K&amp;L GATES</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d14a0ff9f2e641c</t>
+          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, Redshift, Athena, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c20616163c8dea</t>
+          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
         </is>
       </c>
     </row>
@@ -2118,20 +2118,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>iHeartMedia</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>Redshift, RDS, BigQuery, Hive, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ed44d25f7a706b</t>
+          <t>https://www.indeed.com/viewjob?jk=356a68911d5f594b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer (Hybrid)</t>
+          <t>Forward Deployed Software Engineer (FDE), Advanced</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,19 +2176,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191abb774c4fc1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=3cbdae324f66576f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Developer Sr. - AI-Native .NET/ Azure (Cloud Platform)</t>
+          <t>Senior Data Transformation Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Patriot Bank, N.A.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2197,11 +2197,11 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MongoDB, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db55be048a80c25e</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee61801e58afe80</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II - UnderwritingCenter</t>
+          <t>AWS Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b18b7116a0216a</t>
+          <t>https://www.indeed.com/viewjob?jk=df86eb0af63d38af</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - Operational Support (Co-op)</t>
+          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
+          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
+          <t>https://www.indeed.com/viewjob?jk=0d22bd46597ab543</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hartford, CT)</t>
+          <t>Sr Platform Engineer-1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e768638b0d15ea6f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cac895741d0c5e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4d14a0ff9f2e641c</t>
         </is>
       </c>
     </row>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, EMR, Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324abf6ed6a12661</t>
+          <t>https://www.indeed.com/viewjob?jk=20c20616163c8dea</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, CI/CD</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e0436b74d002fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=66ed44d25f7a706b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IT Platform Architect - Network</t>
+          <t>DevOps Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>International Paper</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Splunk, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d26050fc54720f</t>
+          <t>https://www.indeed.com/viewjob?jk=191abb774c4fc1ef</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Product Software Engineer II</t>
+          <t>Software Developer Sr. - AI-Native .NET/ Azure (Cloud Platform)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>Azure, Scala, Kafka, MongoDB, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46198227fa92bca6</t>
+          <t>https://www.indeed.com/viewjob?jk=db55be048a80c25e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Software Engineer II - UnderwritingCenter</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799f6c78471ba72a</t>
+          <t>https://www.indeed.com/viewjob?jk=14b18b7116a0216a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Data Engineer - Operational Support (Co-op)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=495f4d3d488629b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7287ccdf3b9a75d9</t>
+          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer (Hartford, CT)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cain Watters &amp; Associates</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
+          <t>https://www.indeed.com/viewjob?jk=e768638b0d15ea6f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Paylink Direct</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
+          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d48ca7baf014b40f</t>
+          <t>https://www.indeed.com/viewjob?jk=0cac895741d0c5e1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Internship – Data Engineer, Commercial Audience Science (Spring 2027)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Universal Orlando Resort</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, ETL, Power BI, Tableau</t>
+          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c16dbcddbb923</t>
+          <t>https://www.indeed.com/viewjob?jk=324abf6ed6a12661</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer - Fabric</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>GeoLogics Corporation</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
+          <t>https://www.indeed.com/viewjob?jk=b66dbbf4e5b40d68</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Bioinformatics Software Engineer II, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
+          <t>https://www.indeed.com/viewjob?jk=13e882519ae5da00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Product Software Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
+          <t>https://www.indeed.com/viewjob?jk=46198227fa92bca6</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
+          <t>https://www.indeed.com/viewjob?jk=799f6c78471ba72a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
+          <t>https://www.indeed.com/viewjob?jk=495f4d3d488629b9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cain Watters &amp; Associates</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Paylink Direct</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=d48ca7baf014b40f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Internship – Data Engineer, Commercial Audience Science (Spring 2027)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Universal Orlando Resort</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c16dbcddbb923</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Data Engineer - Fabric</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
+          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
+          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
+          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
+          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AmeriGas</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Enterprise Architect, AI Health Cloud</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BrightSpring Health Services</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafad05a90c901ac</t>
+          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=920269b0f09e721a</t>
+          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da2910a4a341974</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b9443c79a19e0d</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88f4a4b03b9105e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec034d4d2c0659b</t>
+          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c012e7a73c63b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AmeriGas</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8efd67ad513c0fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Enterprise Architect, AI Health Cloud</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BrightSpring Health Services</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff87cc807f59577</t>
+          <t>https://www.indeed.com/viewjob?jk=fafad05a90c901ac</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44a0a9b3d5879441</t>
+          <t>https://www.indeed.com/viewjob?jk=920269b0f09e721a</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874c25ddadc07b4c</t>
+          <t>https://www.indeed.com/viewjob?jk=3da2910a4a341974</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf72861040f23682</t>
+          <t>https://www.indeed.com/viewjob?jk=58b9443c79a19e0d</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f24b220aab5d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=b88f4a4b03b9105e</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c249a8e72b3138</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec034d4d2c0659b</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e749bf18c9ccc1</t>
+          <t>https://www.indeed.com/viewjob?jk=c012e7a73c63b98f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Systems Architect</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MACOM Technology Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022e7efd7d261246</t>
+          <t>https://www.indeed.com/viewjob?jk=8efd67ad513c0fe2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MS Fabric</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec086aef45de637</t>
+          <t>https://www.indeed.com/viewjob?jk=8ff87cc807f59577</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb03ca29667d8d5</t>
+          <t>https://www.indeed.com/viewjob?jk=44a0a9b3d5879441</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SQL AND ETL DEVELOPER</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,15 +3986,295 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=874c25ddadc07b4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Software Architect</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf72861040f23682</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Software Architect</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91f24b220aab5d6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Software Architect</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99c249a8e72b3138</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Software Architect</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Annapolis, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3e749bf18c9ccc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Data Systems Architect</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>MACOM Technology Solutions</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Lowell, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=022e7efd7d261246</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>MS Fabric</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ec086aef45de637</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fb03ca29667d8d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SQL AND ETL DEVELOPER</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=de66891cd1166601</t>
         </is>

--- a/results/job_matches_2026-06-13.xlsx
+++ b/results/job_matches_2026-06-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,7 +958,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Hybrid Eligible*)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer (Databricks)</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>QuidelOrtho Corporation</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Latham, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b31d482e2d3c8b</t>
+          <t>https://www.indeed.com/viewjob?jk=30db4d87acabac99</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer (Databricks)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>QuidelOrtho Corporation</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859e7ca77b35594f</t>
+          <t>https://www.indeed.com/viewjob?jk=7edd80e431e58210</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latham, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db4d87acabac99</t>
+          <t>https://www.indeed.com/viewjob?jk=7af97ac7780e4ad6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7edd80e431e58210</t>
+          <t>https://www.indeed.com/viewjob?jk=06003d92ed7c2087</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Midrex Technologies Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7af97ac7780e4ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=06f7fe854f6a6907</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AWS Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Hiring Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6c83582ab47968</t>
+          <t>https://www.indeed.com/viewjob?jk=fc54c80bec441143</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>uShip</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06003d92ed7c2087</t>
+          <t>https://www.indeed.com/viewjob?jk=ae560083a24a530c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Midrex Technologies Inc</t>
+          <t>K&amp;L GATES</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f7fe854f6a6907</t>
+          <t>https://www.indeed.com/viewjob?jk=37aff8f440d6ba6d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AWS Full Stack Software Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hiring Group</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc54c80bec441143</t>
+          <t>https://www.indeed.com/viewjob?jk=6b4b729357fee0da</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>uShip</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae560083a24a530c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5860ee0655d6fc</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b4b729357fee0da</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e67b07fb6f9c29</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5860ee0655d6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebd82ca33ca821</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Data Engineer, Platform Modernization (Data Warehouse Programmer/Analyst)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Caloptima</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e67b07fb6f9c29</t>
+          <t>https://www.indeed.com/viewjob?jk=0dfe4169ae274aad</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Software Engineer, Geospatial Data</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Civitech</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebd82ca33ca821</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d28890cbb8b4f4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer, Platform Modernization (Data Warehouse Programmer/Analyst)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Caloptima</t>
+          <t>Scientific Games</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dfe4169ae274aad</t>
+          <t>https://www.indeed.com/viewjob?jk=418149d6683bca23</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Migration Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37aff8f440d6ba6d</t>
+          <t>https://www.indeed.com/viewjob?jk=88c5b3637f5dab83</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer, Geospatial Data</t>
+          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Civitech</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD</t>
+          <t>AWS, EMR, Redshift, Athena, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d28890cbb8b4f4</t>
+          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Azure &amp; Microsoft Fabric</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Scientific Games</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418149d6683bca23</t>
+          <t>https://www.indeed.com/viewjob?jk=56fe4f99d705b6f4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Application Developer – Data &amp; Digital Solutions</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TC Energy</t>
+          <t>K&amp;L GATES</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b192109a8d9de9</t>
+          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Migration Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c5b3637f5dab83</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd2e06fdde37fe</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure &amp; Microsoft Fabric</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56fe4f99d705b6f4</t>
+          <t>https://www.indeed.com/viewjob?jk=adebbeb79bcc9a1c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd2e06fdde37fe</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9760e71980916f</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adebbeb79bcc9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=94cb48d5ed1c52af</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9760e71980916f</t>
+          <t>https://www.indeed.com/viewjob?jk=fbc89f3bdee8ad93</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94cb48d5ed1c52af</t>
+          <t>https://www.indeed.com/viewjob?jk=4c02b3eae0c4832e</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbc89f3bdee8ad93</t>
+          <t>https://www.indeed.com/viewjob?jk=da723ed84459a1ba</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c02b3eae0c4832e</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2dcb8f1f90f8bd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Forward Deployed Software Engineer (FDE), Advanced</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da723ed84459a1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=3cbdae324f66576f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Transformation Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Patriot Bank, N.A.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2dcb8f1f90f8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee61801e58afe80</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Dimensional Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
+          <t>https://www.indeed.com/viewjob?jk=0d22bd46597ab543</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>iHeartMedia</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hive, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, EMR, Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356a68911d5f594b</t>
+          <t>https://www.indeed.com/viewjob?jk=20c20616163c8dea</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE), Advanced</t>
+          <t>Sr Platform Engineer-1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cbdae324f66576f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Transformation Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Patriot Bank, N.A.</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee61801e58afe80</t>
+          <t>https://www.indeed.com/viewjob?jk=4d14a0ff9f2e641c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AWS Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df86eb0af63d38af</t>
+          <t>https://www.indeed.com/viewjob?jk=66ed44d25f7a706b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
+          <t>DevOps Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
+          <t>https://www.indeed.com/viewjob?jk=191abb774c4fc1ef</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Software Developer Sr. - AI-Native .NET/ Azure (Cloud Platform)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, CI/CD</t>
+          <t>Azure, Scala, Kafka, MongoDB, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d22bd46597ab543</t>
+          <t>https://www.indeed.com/viewjob?jk=db55be048a80c25e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer-1</t>
+          <t>Software Engineer II - UnderwritingCenter</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Flexential</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=14b18b7116a0216a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer (Hartford, CT)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d14a0ff9f2e641c</t>
+          <t>https://www.indeed.com/viewjob?jk=e768638b0d15ea6f</t>
         </is>
       </c>
     </row>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c20616163c8dea</t>
+          <t>https://www.indeed.com/viewjob?jk=0cac895741d0c5e1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ed44d25f7a706b</t>
+          <t>https://www.indeed.com/viewjob?jk=324abf6ed6a12661</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer (Hybrid)</t>
+          <t>Data Engineer - Operational Support (Co-op)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191abb774c4fc1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Developer Sr. - AI-Native .NET/ Azure (Cloud Platform)</t>
+          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MongoDB, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,59 +2526,59 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db55be048a80c25e</t>
+          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer II - UnderwritingCenter</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b18b7116a0216a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0905912913a35c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer - Operational Support (Co-op)</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
+          <t>https://www.indeed.com/viewjob?jk=eb5b987c1cb763e9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
+          <t>https://www.indeed.com/viewjob?jk=19fa9727f194c93a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hartford, CT)</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e768638b0d15ea6f</t>
+          <t>https://www.indeed.com/viewjob?jk=f89fd566c7357b0a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cac895741d0c5e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c0be12bfd78e5a42</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324abf6ed6a12661</t>
+          <t>https://www.indeed.com/viewjob?jk=fa18885de990da95</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cain Watters &amp; Associates</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
+          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Paylink Direct</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d48ca7baf014b40f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Internship – Data Engineer, Commercial Audience Science (Spring 2027)</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Universal Orlando Resort</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c16dbcddbb923</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer - Fabric</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,24 +3041,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
+          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
+          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
+          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
+          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
+          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>AmeriGas</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cain Watters &amp; Associates</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
+          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Paylink Direct</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
+          <t>https://www.indeed.com/viewjob?jk=d48ca7baf014b40f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Data Engineer - Fabric</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AmeriGas</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
+          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
         </is>
       </c>
     </row>
@@ -4143,17 +4143,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Systems Architect</t>
+          <t>MS Fabric</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MACOM Technology Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022e7efd7d261246</t>
+          <t>https://www.indeed.com/viewjob?jk=6ec086aef45de637</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MS Fabric</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec086aef45de637</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb03ca29667d8d5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>SQL AND ETL DEVELOPER</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4240,41 +4240,6 @@
         </is>
       </c>
       <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb03ca29667d8d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>SQL AND ETL DEVELOPER</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=de66891cd1166601</t>
         </is>

--- a/results/job_matches_2026-06-13.xlsx
+++ b/results/job_matches_2026-06-13.xlsx
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37aff8f440d6ba6d</t>
+          <t>https://www.indeed.com/viewjob?jk=6b4b729357fee0da</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b4b729357fee0da</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5860ee0655d6fc</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5860ee0655d6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e67b07fb6f9c29</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e67b07fb6f9c29</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebd82ca33ca821</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Data Engineer, Platform Modernization (Data Warehouse Programmer/Analyst)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Caloptima</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebd82ca33ca821</t>
+          <t>https://www.indeed.com/viewjob?jk=0dfe4169ae274aad</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer, Platform Modernization (Data Warehouse Programmer/Analyst)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Caloptima</t>
+          <t>K&amp;L GATES</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dfe4169ae274aad</t>
+          <t>https://www.indeed.com/viewjob?jk=37aff8f440d6ba6d</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
+          <t>Data Engineer - Azure &amp; Microsoft Fabric</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
+          <t>https://www.indeed.com/viewjob?jk=56fe4f99d705b6f4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure &amp; Microsoft Fabric</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56fe4f99d705b6f4</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd2e06fdde37fe</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Dimensional Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=adebbeb79bcc9a1c</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd2e06fdde37fe</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9760e71980916f</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adebbeb79bcc9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=94cb48d5ed1c52af</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9760e71980916f</t>
+          <t>https://www.indeed.com/viewjob?jk=fbc89f3bdee8ad93</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94cb48d5ed1c52af</t>
+          <t>https://www.indeed.com/viewjob?jk=4c02b3eae0c4832e</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbc89f3bdee8ad93</t>
+          <t>https://www.indeed.com/viewjob?jk=da723ed84459a1ba</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c02b3eae0c4832e</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2dcb8f1f90f8bd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>K&amp;L GATES</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da723ed84459a1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, EMR, Redshift, Athena, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2dcb8f1f90f8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Transformation Data Architect</t>
+          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Patriot Bank, N.A.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee61801e58afe80</t>
+          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
+          <t>Senior Data Transformation Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Patriot Bank, N.A.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee61801e58afe80</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr Platform Engineer-1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c20616163c8dea</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer-1</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Flexential</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=4d14a0ff9f2e641c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, EMR, Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d14a0ff9f2e641c</t>
+          <t>https://www.indeed.com/viewjob?jk=20c20616163c8dea</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hartford, CT)</t>
+          <t>Data Engineer - Operational Support (Co-op)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e768638b0d15ea6f</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cac895741d0c5e1</t>
+          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Data Engineer (Hartford, CT)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324abf6ed6a12661</t>
+          <t>https://www.indeed.com/viewjob?jk=e768638b0d15ea6f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Operational Support (Co-op)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
+          <t>https://www.indeed.com/viewjob?jk=0cac895741d0c5e1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
+          <t>https://www.indeed.com/viewjob?jk=324abf6ed6a12661</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer II, Pathology and Lab Medicine</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e882519ae5da00</t>
+          <t>https://www.indeed.com/viewjob?jk=495f4d3d488629b9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Product Software Engineer II</t>
+          <t>Bioinformatics Software Engineer II, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46198227fa92bca6</t>
+          <t>https://www.indeed.com/viewjob?jk=13e882519ae5da00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Product Software Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799f6c78471ba72a</t>
+          <t>https://www.indeed.com/viewjob?jk=46198227fa92bca6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=495f4d3d488629b9</t>
+          <t>https://www.indeed.com/viewjob?jk=799f6c78471ba72a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
+          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cain Watters &amp; Associates</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
+          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Paylink Direct</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
+          <t>https://www.indeed.com/viewjob?jk=d48ca7baf014b40f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Data Engineer - Fabric</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,24 +3041,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
+          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
+          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
+          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
+          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
+          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
+          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AmeriGas</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cain Watters &amp; Associates</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
+          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Paylink Direct</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d48ca7baf014b40f</t>
+          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer - Fabric</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>AmeriGas</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
+          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
         </is>
       </c>
     </row>
@@ -4178,17 +4178,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>SQL AND ETL DEVELOPER</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb03ca29667d8d5</t>
+          <t>https://www.indeed.com/viewjob?jk=de66891cd1166601</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SQL AND ETL DEVELOPER</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de66891cd1166601</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb03ca29667d8d5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-13.xlsx
+++ b/results/job_matches_2026-06-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c20616163c8dea</t>
+          <t>https://www.indeed.com/viewjob?jk=66ed44d25f7a706b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ed44d25f7a706b</t>
+          <t>https://www.indeed.com/viewjob?jk=191abb774c4fc1ef</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer (Hybrid)</t>
+          <t>Software Developer Sr. - AI-Native .NET/ Azure (Cloud Platform)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>Azure, Scala, Kafka, MongoDB, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191abb774c4fc1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=db55be048a80c25e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Developer Sr. - AI-Native .NET/ Azure (Cloud Platform)</t>
+          <t>Software Engineer II - UnderwritingCenter</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MongoDB, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db55be048a80c25e</t>
+          <t>https://www.indeed.com/viewjob?jk=14b18b7116a0216a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer II - UnderwritingCenter</t>
+          <t>Data Engineer - Operational Support (Co-op)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b18b7116a0216a</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - Operational Support (Co-op)</t>
+          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
+          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
+          <t>Sr. Data Engineer (Hartford, CT)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e768638b0d15ea6f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hartford, CT)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e768638b0d15ea6f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0905912913a35c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cac895741d0c5e1</t>
+          <t>https://www.indeed.com/viewjob?jk=eb5b987c1cb763e9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,24 +2516,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324abf6ed6a12661</t>
+          <t>https://www.indeed.com/viewjob?jk=19fa9727f194c93a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0905912913a35c</t>
+          <t>https://www.indeed.com/viewjob?jk=f89fd566c7357b0a</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb5b987c1cb763e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c0be12bfd78e5a42</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19fa9727f194c93a</t>
+          <t>https://www.indeed.com/viewjob?jk=fa18885de990da95</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>GeoLogics Corporation</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89fd566c7357b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=b66dbbf4e5b40d68</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0be12bfd78e5a42</t>
+          <t>https://www.indeed.com/viewjob?jk=495f4d3d488629b9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Bioinformatics Software Engineer II, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,77 +2726,77 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa18885de990da95</t>
+          <t>https://www.indeed.com/viewjob?jk=13e882519ae5da00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GeoLogics Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66dbbf4e5b40d68</t>
+          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Cain Watters &amp; Associates</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=495f4d3d488629b9</t>
+          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer II, Pathology and Lab Medicine</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Paylink Direct</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e882519ae5da00</t>
+          <t>https://www.indeed.com/viewjob?jk=d48ca7baf014b40f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Product Software Engineer II</t>
+          <t>Data Engineer - Fabric</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46198227fa92bca6</t>
+          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799f6c78471ba72a</t>
+          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cain Watters &amp; Associates</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Paylink Direct</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d48ca7baf014b40f</t>
+          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer - Fabric</t>
+          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
+          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
+          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
+          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
+          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
+          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
+          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>AmeriGas</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Enterprise Architect, AI Health Cloud</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BrightSpring Health Services</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
+          <t>https://www.indeed.com/viewjob?jk=fafad05a90c901ac</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
+          <t>https://www.indeed.com/viewjob?jk=920269b0f09e721a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
+          <t>https://www.indeed.com/viewjob?jk=3da2910a4a341974</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
+          <t>https://www.indeed.com/viewjob?jk=58b9443c79a19e0d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AmeriGas</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
+          <t>https://www.indeed.com/viewjob?jk=b88f4a4b03b9105e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Enterprise Architect, AI Health Cloud</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BrightSpring Health Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafad05a90c901ac</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec034d4d2c0659b</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=920269b0f09e721a</t>
+          <t>https://www.indeed.com/viewjob?jk=c012e7a73c63b98f</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da2910a4a341974</t>
+          <t>https://www.indeed.com/viewjob?jk=8efd67ad513c0fe2</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b9443c79a19e0d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ff87cc807f59577</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88f4a4b03b9105e</t>
+          <t>https://www.indeed.com/viewjob?jk=44a0a9b3d5879441</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec034d4d2c0659b</t>
+          <t>https://www.indeed.com/viewjob?jk=874c25ddadc07b4c</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c012e7a73c63b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=bf72861040f23682</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8efd67ad513c0fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=91f24b220aab5d6c</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff87cc807f59577</t>
+          <t>https://www.indeed.com/viewjob?jk=99c249a8e72b3138</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44a0a9b3d5879441</t>
+          <t>https://www.indeed.com/viewjob?jk=a3e749bf18c9ccc1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>MS Fabric</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874c25ddadc07b4c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ec086aef45de637</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>SQL AND ETL DEVELOPER</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,217 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf72861040f23682</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91f24b220aab5d6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99c249a8e72b3138</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Annapolis, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e749bf18c9ccc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>MS Fabric</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec086aef45de637</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>SQL AND ETL DEVELOPER</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=de66891cd1166601</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb03ca29667d8d5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-13.xlsx
+++ b/results/job_matches_2026-06-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Experienced AWS Solutions Architect and Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Kaizen Analytix LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9e656d2a85bee5</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f364a3ec32fde4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Experienced AWS Solutions Architect and Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kaizen Analytix LLC</t>
+          <t>Brookfield Properties</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM, RDS</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f364a3ec32fde4</t>
+          <t>https://www.indeed.com/viewjob?jk=eb497e82428572d4</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Brookfield Properties</t>
+          <t>WaFd Bank</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb497e82428572d4</t>
+          <t>https://www.indeed.com/viewjob?jk=c1dd83ec2340a8ca</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Python &amp; SAS Developer (Data Modernization)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WaFd Bank</t>
+          <t>Illumen Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dd83ec2340a8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d892ead602b58795</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Python &amp; SAS Developer (Data Modernization)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Illumen Group</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d892ead602b58795</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6c83582ab47968</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>AI/ML Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>QuidelOrtho Corporation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latham, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db4d87acabac99</t>
+          <t>https://www.indeed.com/viewjob?jk=83b31d482e2d3c8b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>QuidelOrtho Corporation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7edd80e431e58210</t>
+          <t>https://www.indeed.com/viewjob?jk=859e7ca77b35594f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Latham, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7af97ac7780e4ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=30db4d87acabac99</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06003d92ed7c2087</t>
+          <t>https://www.indeed.com/viewjob?jk=7edd80e431e58210</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Midrex Technologies Inc</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f7fe854f6a6907</t>
+          <t>https://www.indeed.com/viewjob?jk=7af97ac7780e4ad6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AWS Full Stack Software Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hiring Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc54c80bec441143</t>
+          <t>https://www.indeed.com/viewjob?jk=06003d92ed7c2087</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>uShip</t>
+          <t>Midrex Technologies Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae560083a24a530c</t>
+          <t>https://www.indeed.com/viewjob?jk=06f7fe854f6a6907</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>DEVOPS ENGINEER</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NYC Human Resources Administration</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, ELT, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b4b729357fee0da</t>
+          <t>https://www.indeed.com/viewjob?jk=1766fc067ea2cb5c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Senior AWS Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Hiring Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5860ee0655d6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=fc54c80bec441143</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>uShip</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e67b07fb6f9c29</t>
+          <t>https://www.indeed.com/viewjob?jk=ae560083a24a530c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>K&amp;L GATES</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebd82ca33ca821</t>
+          <t>https://www.indeed.com/viewjob?jk=37aff8f440d6ba6d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer, Platform Modernization (Data Warehouse Programmer/Analyst)</t>
+          <t>Sr. Data Engineer - Ag &amp; Trading</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Caloptima</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dfe4169ae274aad</t>
+          <t>https://www.indeed.com/viewjob?jk=a8edb3b00b860017</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37aff8f440d6ba6d</t>
+          <t>https://www.indeed.com/viewjob?jk=6b4b729357fee0da</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer, Geospatial Data</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Civitech</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d28890cbb8b4f4</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5860ee0655d6fc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Scientific Games</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418149d6683bca23</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e67b07fb6f9c29</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Migration Architect</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c5b3637f5dab83</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebd82ca33ca821</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure &amp; Microsoft Fabric</t>
+          <t>Data Engineer, Platform Modernization (Data Warehouse Programmer/Analyst)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Caloptima</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56fe4f99d705b6f4</t>
+          <t>https://www.indeed.com/viewjob?jk=0dfe4169ae274aad</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer, Geospatial Data</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Civitech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd2e06fdde37fe</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d28890cbb8b4f4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Scientific Games</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adebbeb79bcc9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=418149d6683bca23</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Migration Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9760e71980916f</t>
+          <t>https://www.indeed.com/viewjob?jk=88c5b3637f5dab83</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, EMR, Redshift, Athena, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94cb48d5ed1c52af</t>
+          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer - Azure &amp; Microsoft Fabric</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbc89f3bdee8ad93</t>
+          <t>https://www.indeed.com/viewjob?jk=56fe4f99d705b6f4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>iHeartMedia</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>Redshift, RDS, BigQuery, Hive, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c02b3eae0c4832e</t>
+          <t>https://www.indeed.com/viewjob?jk=356a68911d5f594b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>K&amp;L GATES</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da723ed84459a1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2dcb8f1f90f8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd2e06fdde37fe</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Dimensional Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=adebbeb79bcc9a1c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9760e71980916f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE), Advanced</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cbdae324f66576f</t>
+          <t>https://www.indeed.com/viewjob?jk=94cb48d5ed1c52af</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
+          <t>https://www.indeed.com/viewjob?jk=fbc89f3bdee8ad93</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Transformation Data Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Patriot Bank, N.A.</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee61801e58afe80</t>
+          <t>https://www.indeed.com/viewjob?jk=4c02b3eae0c4832e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d22bd46597ab543</t>
+          <t>https://www.indeed.com/viewjob?jk=da723ed84459a1ba</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer-1</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Flexential</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2dcb8f1f90f8bd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployed Software Engineer (FDE), Advanced</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d14a0ff9f2e641c</t>
+          <t>https://www.indeed.com/viewjob?jk=3cbdae324f66576f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ed44d25f7a706b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer (Hybrid)</t>
+          <t>Senior Data Transformation Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Patriot Bank, N.A.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191abb774c4fc1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee61801e58afe80</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Developer Sr. - AI-Native .NET/ Azure (Cloud Platform)</t>
+          <t>Sr Platform Engineer-1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MongoDB, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db55be048a80c25e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer II - UnderwritingCenter</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b18b7116a0216a</t>
+          <t>https://www.indeed.com/viewjob?jk=4d14a0ff9f2e641c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer - Operational Support (Co-op)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
+          <t>https://www.indeed.com/viewjob?jk=66ed44d25f7a706b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
+          <t>DevOps Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
+          <t>https://www.indeed.com/viewjob?jk=191abb774c4fc1ef</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hartford, CT)</t>
+          <t>Software Developer Sr. - AI-Native .NET/ Azure (Cloud Platform)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>Azure, Scala, Kafka, MongoDB, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,59 +2421,59 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e768638b0d15ea6f</t>
+          <t>https://www.indeed.com/viewjob?jk=db55be048a80c25e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Software Engineer II - UnderwritingCenter</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0905912913a35c</t>
+          <t>https://www.indeed.com/viewjob?jk=14b18b7116a0216a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Data Engineer - Operational Support (Co-op)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb5b987c1cb763e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,24 +2516,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19fa9727f194c93a</t>
+          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89fd566c7357b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0905912913a35c</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0be12bfd78e5a42</t>
+          <t>https://www.indeed.com/viewjob?jk=eb5b987c1cb763e9</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa18885de990da95</t>
+          <t>https://www.indeed.com/viewjob?jk=19fa9727f194c93a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GeoLogics Corporation</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66dbbf4e5b40d68</t>
+          <t>https://www.indeed.com/viewjob?jk=f89fd566c7357b0a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=495f4d3d488629b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c0be12bfd78e5a42</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer II, Pathology and Lab Medicine</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,77 +2726,77 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e882519ae5da00</t>
+          <t>https://www.indeed.com/viewjob?jk=fa18885de990da95</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GeoLogics Corporation</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
+          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
+          <t>https://www.indeed.com/viewjob?jk=b66dbbf4e5b40d68</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Bioinformatics Software Engineer II, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cain Watters &amp; Associates</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
+          <t>https://www.indeed.com/viewjob?jk=13e882519ae5da00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Paylink Direct</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d48ca7baf014b40f</t>
+          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer - Fabric</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
+          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
+          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
+          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
+          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
+          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>AmeriGas</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
+          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AmeriGas</t>
+          <t>Cain Watters &amp; Associates</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
+          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Enterprise Architect, AI Health Cloud</t>
+          <t>Data Engineer - Fabric</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BrightSpring Health Services</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafad05a90c901ac</t>
+          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Enterprise Architect, AI Health Cloud</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BrightSpring Health Services</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=920269b0f09e721a</t>
+          <t>https://www.indeed.com/viewjob?jk=fafad05a90c901ac</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da2910a4a341974</t>
+          <t>https://www.indeed.com/viewjob?jk=920269b0f09e721a</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b9443c79a19e0d</t>
+          <t>https://www.indeed.com/viewjob?jk=3da2910a4a341974</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88f4a4b03b9105e</t>
+          <t>https://www.indeed.com/viewjob?jk=58b9443c79a19e0d</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec034d4d2c0659b</t>
+          <t>https://www.indeed.com/viewjob?jk=b88f4a4b03b9105e</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c012e7a73c63b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec034d4d2c0659b</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8efd67ad513c0fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=c012e7a73c63b98f</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff87cc807f59577</t>
+          <t>https://www.indeed.com/viewjob?jk=8efd67ad513c0fe2</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44a0a9b3d5879441</t>
+          <t>https://www.indeed.com/viewjob?jk=8ff87cc807f59577</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874c25ddadc07b4c</t>
+          <t>https://www.indeed.com/viewjob?jk=44a0a9b3d5879441</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf72861040f23682</t>
+          <t>https://www.indeed.com/viewjob?jk=874c25ddadc07b4c</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f24b220aab5d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=bf72861040f23682</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c249a8e72b3138</t>
+          <t>https://www.indeed.com/viewjob?jk=91f24b220aab5d6c</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e749bf18c9ccc1</t>
+          <t>https://www.indeed.com/viewjob?jk=99c249a8e72b3138</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MS Fabric</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec086aef45de637</t>
+          <t>https://www.indeed.com/viewjob?jk=a3e749bf18c9ccc1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SQL AND ETL DEVELOPER</t>
+          <t>MS Fabric</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,15 +4021,50 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ec086aef45de637</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SQL AND ETL DEVELOPER</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=de66891cd1166601</t>
         </is>

--- a/results/job_matches_2026-06-13.xlsx
+++ b/results/job_matches_2026-06-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Migration Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Scientific Games</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418149d6683bca23</t>
+          <t>https://www.indeed.com/viewjob?jk=88c5b3637f5dab83</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Migration Architect</t>
+          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, EMR, Redshift, Athena, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c5b3637f5dab83</t>
+          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
+          <t>Data Engineer - Azure &amp; Microsoft Fabric</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
+          <t>https://www.indeed.com/viewjob?jk=56fe4f99d705b6f4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure &amp; Microsoft Fabric</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>iHeartMedia</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>Redshift, RDS, BigQuery, Hive, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56fe4f99d705b6f4</t>
+          <t>https://www.indeed.com/viewjob?jk=356a68911d5f594b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>iHeartMedia</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hive, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356a68911d5f594b</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd2e06fdde37fe</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Dimensional Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=adebbeb79bcc9a1c</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd2e06fdde37fe</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9760e71980916f</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adebbeb79bcc9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=94cb48d5ed1c52af</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9760e71980916f</t>
+          <t>https://www.indeed.com/viewjob?jk=fbc89f3bdee8ad93</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94cb48d5ed1c52af</t>
+          <t>https://www.indeed.com/viewjob?jk=4c02b3eae0c4832e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbc89f3bdee8ad93</t>
+          <t>https://www.indeed.com/viewjob?jk=da723ed84459a1ba</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c02b3eae0c4832e</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2dcb8f1f90f8bd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Forward Deployed Software Engineer (FDE), Advanced</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da723ed84459a1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=3cbdae324f66576f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Transformation Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Patriot Bank, N.A.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2dcb8f1f90f8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee61801e58afe80</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE), Advanced</t>
+          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cbdae324f66576f</t>
+          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
+          <t>Sr Platform Engineer-1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Transformation Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Patriot Bank, N.A.</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee61801e58afe80</t>
+          <t>https://www.indeed.com/viewjob?jk=4d14a0ff9f2e641c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer-1</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Flexential</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=66ed44d25f7a706b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d14a0ff9f2e641c</t>
+          <t>https://www.indeed.com/viewjob?jk=191abb774c4fc1ef</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Operational Support (Co-op)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ed44d25f7a706b</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer (Hybrid)</t>
+          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,94 +2386,94 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191abb774c4fc1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Developer Sr. - AI-Native .NET/ Azure (Cloud Platform)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MongoDB, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db55be048a80c25e</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0905912913a35c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer II - UnderwritingCenter</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b18b7116a0216a</t>
+          <t>https://www.indeed.com/viewjob?jk=eb5b987c1cb763e9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Operational Support (Co-op)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
+          <t>https://www.indeed.com/viewjob?jk=19fa9727f194c93a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,24 +2516,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f89fd566c7357b0a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0905912913a35c</t>
+          <t>https://www.indeed.com/viewjob?jk=c0be12bfd78e5a42</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb5b987c1cb763e9</t>
+          <t>https://www.indeed.com/viewjob?jk=fa18885de990da95</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>GeoLogics Corporation</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19fa9727f194c93a</t>
+          <t>https://www.indeed.com/viewjob?jk=b66dbbf4e5b40d68</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Bioinformatics Software Engineer II, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,147 +2656,147 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89fd566c7357b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=13e882519ae5da00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0be12bfd78e5a42</t>
+          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa18885de990da95</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GeoLogics Corporation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66dbbf4e5b40d68</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer II, Pathology and Lab Medicine</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e882519ae5da00</t>
+          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
+          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
+          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
+          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
+          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>AmeriGas</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cain Watters &amp; Associates</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
+          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
+          <t>Data Engineer - Fabric</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
+          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Enterprise Architect, AI Health Cloud</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AmeriGas</t>
+          <t>BrightSpring Health Services</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
+          <t>https://www.indeed.com/viewjob?jk=fafad05a90c901ac</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
+          <t>https://www.indeed.com/viewjob?jk=920269b0f09e721a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cain Watters &amp; Associates</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
+          <t>https://www.indeed.com/viewjob?jk=3da2910a4a341974</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer - Fabric</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
+          <t>https://www.indeed.com/viewjob?jk=58b9443c79a19e0d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Enterprise Architect, AI Health Cloud</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BrightSpring Health Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafad05a90c901ac</t>
+          <t>https://www.indeed.com/viewjob?jk=b88f4a4b03b9105e</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=920269b0f09e721a</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec034d4d2c0659b</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da2910a4a341974</t>
+          <t>https://www.indeed.com/viewjob?jk=c012e7a73c63b98f</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b9443c79a19e0d</t>
+          <t>https://www.indeed.com/viewjob?jk=8efd67ad513c0fe2</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88f4a4b03b9105e</t>
+          <t>https://www.indeed.com/viewjob?jk=8ff87cc807f59577</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec034d4d2c0659b</t>
+          <t>https://www.indeed.com/viewjob?jk=44a0a9b3d5879441</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c012e7a73c63b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=874c25ddadc07b4c</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8efd67ad513c0fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=bf72861040f23682</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff87cc807f59577</t>
+          <t>https://www.indeed.com/viewjob?jk=91f24b220aab5d6c</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44a0a9b3d5879441</t>
+          <t>https://www.indeed.com/viewjob?jk=99c249a8e72b3138</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874c25ddadc07b4c</t>
+          <t>https://www.indeed.com/viewjob?jk=a3e749bf18c9ccc1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>MS Fabric</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf72861040f23682</t>
+          <t>https://www.indeed.com/viewjob?jk=6ec086aef45de637</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>SQL AND ETL DEVELOPER</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3925,146 +3925,6 @@
         </is>
       </c>
       <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91f24b220aab5d6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99c249a8e72b3138</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Annapolis, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e749bf18c9ccc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>MS Fabric</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec086aef45de637</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>SQL AND ETL DEVELOPER</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=de66891cd1166601</t>
         </is>

--- a/results/job_matches_2026-06-13.xlsx
+++ b/results/job_matches_2026-06-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ProcyonIT</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=816452e4692ec940</t>
+          <t>https://www.indeed.com/viewjob?jk=f08447131564025e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Java - International Card Risk Services Technology</t>
+          <t>Data Engineer, Mid</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Acentra Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, GCP, HBase, Scala, Kafka, Oracle</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea3d9a3991748c</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6f9d2703398a29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Data Architect</t>
+          <t>Data &amp; Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, Unity Catalog, Spark, PySpark, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08447131564025e</t>
+          <t>https://www.indeed.com/viewjob?jk=8627b9fa5d939b34</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer, Mid</t>
+          <t>Senior Cloud Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Acentra Health</t>
+          <t>Intelex</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, S3, ECS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6f9d2703398a29</t>
+          <t>https://www.indeed.com/viewjob?jk=f9addd16d08dc466</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data &amp; Software Engineer</t>
+          <t>Senior Cybersecurity Data Engineer - AI/ML SME</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, Unity Catalog, Spark, PySpark, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, EMR, Kinesis, RDS, Spark, Scala, Kafka, Dask, ETL, MLOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8627b9fa5d939b34</t>
+          <t>https://www.indeed.com/viewjob?jk=599be78bf8533a28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud Architect</t>
+          <t>Experienced AWS Solutions Architect and Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Intelex</t>
+          <t>Kaizen Analytix LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9addd16d08dc466</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f364a3ec32fde4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer - AI/ML SME</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Brookfield Properties</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, RDS, Spark, Scala, Kafka, Dask, ETL, MLOps</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599be78bf8533a28</t>
+          <t>https://www.indeed.com/viewjob?jk=eb497e82428572d4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Experienced AWS Solutions Architect and Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kaizen Analytix LLC</t>
+          <t>WaFd Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM, RDS</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f364a3ec32fde4</t>
+          <t>https://www.indeed.com/viewjob?jk=c1dd83ec2340a8ca</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Python &amp; SAS Developer (Data Modernization)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Brookfield Properties</t>
+          <t>Illumen Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb497e82428572d4</t>
+          <t>https://www.indeed.com/viewjob?jk=d892ead602b58795</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WaFd Bank</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dd83ec2340a8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6c83582ab47968</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Python &amp; SAS Developer (Data Modernization)</t>
+          <t>AI/ML Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Illumen Group</t>
+          <t>QuidelOrtho Corporation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Spark, PySpark, Scala, Oracle</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d892ead602b58795</t>
+          <t>https://www.indeed.com/viewjob?jk=83b31d482e2d3c8b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI/ML Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>QuidelOrtho Corporation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6c83582ab47968</t>
+          <t>https://www.indeed.com/viewjob?jk=859e7ca77b35594f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer (Databricks)</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>QuidelOrtho Corporation</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Latham, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b31d482e2d3c8b</t>
+          <t>https://www.indeed.com/viewjob?jk=30db4d87acabac99</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer (Databricks)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>QuidelOrtho Corporation</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859e7ca77b35594f</t>
+          <t>https://www.indeed.com/viewjob?jk=7edd80e431e58210</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latham, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db4d87acabac99</t>
+          <t>https://www.indeed.com/viewjob?jk=7af97ac7780e4ad6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Midrex Technologies Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7edd80e431e58210</t>
+          <t>https://www.indeed.com/viewjob?jk=06f7fe854f6a6907</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DEVOPS ENGINEER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NYC Human Resources Administration</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, ELT, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7af97ac7780e4ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=1766fc067ea2cb5c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior AWS Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hiring Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06003d92ed7c2087</t>
+          <t>https://www.indeed.com/viewjob?jk=fc54c80bec441143</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Midrex Technologies Inc</t>
+          <t>uShip</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f7fe854f6a6907</t>
+          <t>https://www.indeed.com/viewjob?jk=ae560083a24a530c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DEVOPS ENGINEER</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NYC Human Resources Administration</t>
+          <t>K&amp;L GATES</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, ELT, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1766fc067ea2cb5c</t>
+          <t>https://www.indeed.com/viewjob?jk=37aff8f440d6ba6d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AWS Full Stack Software Engineer</t>
+          <t>Sr. Data Engineer - Ag &amp; Trading</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hiring Group</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc54c80bec441143</t>
+          <t>https://www.indeed.com/viewjob?jk=a8edb3b00b860017</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>uShip</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae560083a24a530c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b4b729357fee0da</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,19 +1406,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37aff8f440d6ba6d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5860ee0655d6fc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Ag &amp; Trading</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8edb3b00b860017</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e67b07fb6f9c29</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b4b729357fee0da</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebd82ca33ca821</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Data Engineer, Platform Modernization (Data Warehouse Programmer/Analyst)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Caloptima</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5860ee0655d6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=0dfe4169ae274aad</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Software Engineer, Geospatial Data</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Civitech</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e67b07fb6f9c29</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d28890cbb8b4f4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Senior Migration Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebd82ca33ca821</t>
+          <t>https://www.indeed.com/viewjob?jk=88c5b3637f5dab83</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer, Platform Modernization (Data Warehouse Programmer/Analyst)</t>
+          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Caloptima</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, EMR, Redshift, Athena, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dfe4169ae274aad</t>
+          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer, Geospatial Data</t>
+          <t>Data Engineer - Azure &amp; Microsoft Fabric</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Civitech</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d28890cbb8b4f4</t>
+          <t>https://www.indeed.com/viewjob?jk=56fe4f99d705b6f4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Migration Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>iHeartMedia</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>Redshift, RDS, BigQuery, Hive, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c5b3637f5dab83</t>
+          <t>https://www.indeed.com/viewjob?jk=356a68911d5f594b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
+          <t>Forward Deployed Software Engineer (FDE), Advanced</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
+          <t>https://www.indeed.com/viewjob?jk=3cbdae324f66576f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure &amp; Microsoft Fabric</t>
+          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56fe4f99d705b6f4</t>
+          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Transformation Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>iHeartMedia</t>
+          <t>Patriot Bank, N.A.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hive, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356a68911d5f594b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee61801e58afe80</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Platform Engineer-1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd2e06fdde37fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adebbeb79bcc9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=4d14a0ff9f2e641c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,277 +1896,277 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9760e71980916f</t>
+          <t>https://www.indeed.com/viewjob?jk=66ed44d25f7a706b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94cb48d5ed1c52af</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0905912913a35c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbc89f3bdee8ad93</t>
+          <t>https://www.indeed.com/viewjob?jk=eb5b987c1cb763e9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c02b3eae0c4832e</t>
+          <t>https://www.indeed.com/viewjob?jk=19fa9727f194c93a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da723ed84459a1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f89fd566c7357b0a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2dcb8f1f90f8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c0be12bfd78e5a42</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE), Advanced</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cbdae324f66576f</t>
+          <t>https://www.indeed.com/viewjob?jk=fa18885de990da95</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Transformation Data Architect</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Patriot Bank, N.A.</t>
+          <t>GeoLogics Corporation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee61801e58afe80</t>
+          <t>https://www.indeed.com/viewjob?jk=b66dbbf4e5b40d68</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
+          <t>Bioinformatics Software Engineer II, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
+          <t>https://www.indeed.com/viewjob?jk=13e882519ae5da00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer-1</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Flexential</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d14a0ff9f2e641c</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ed44d25f7a706b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer (Hybrid)</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191abb774c4fc1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer - Operational Support (Co-op)</t>
+          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
+          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,277 +2386,277 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0905912913a35c</t>
+          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb5b987c1cb763e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19fa9727f194c93a</t>
+          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89fd566c7357b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0be12bfd78e5a42</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa18885de990da95</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GeoLogics Corporation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66dbbf4e5b40d68</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer II, Pathology and Lab Medicine</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e882519ae5da00</t>
+          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
+          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
+          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cain Watters &amp; Associates</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
+          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Data Engineer - Fabric</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
+          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
+          <t>Enterprise Architect, AI Health Cloud</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BrightSpring Health Services</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
+          <t>https://www.indeed.com/viewjob?jk=fafad05a90c901ac</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=920269b0f09e721a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=3da2910a4a341974</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
+          <t>https://www.indeed.com/viewjob?jk=58b9443c79a19e0d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
+          <t>https://www.indeed.com/viewjob?jk=b88f4a4b03b9105e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec034d4d2c0659b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
+          <t>https://www.indeed.com/viewjob?jk=c012e7a73c63b98f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
+          <t>https://www.indeed.com/viewjob?jk=8efd67ad513c0fe2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
+          <t>https://www.indeed.com/viewjob?jk=8ff87cc807f59577</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
+          <t>https://www.indeed.com/viewjob?jk=44a0a9b3d5879441</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
+          <t>https://www.indeed.com/viewjob?jk=874c25ddadc07b4c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AmeriGas</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
+          <t>https://www.indeed.com/viewjob?jk=bf72861040f23682</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
+          <t>https://www.indeed.com/viewjob?jk=91f24b220aab5d6c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>MS Fabric</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cain Watters &amp; Associates</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,637 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Data Engineer - Fabric</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>JSR Tech Consulting</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Enterprise Architect, AI Health Cloud</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>BrightSpring Health Services</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fafad05a90c901ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=920269b0f09e721a</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3da2910a4a341974</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Springfield, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58b9443c79a19e0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b88f4a4b03b9105e</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec034d4d2c0659b</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c012e7a73c63b98f</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Albany, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8efd67ad513c0fe2</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Trenton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff87cc807f59577</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Providence, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44a0a9b3d5879441</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=874c25ddadc07b4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Little Rock, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf72861040f23682</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91f24b220aab5d6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99c249a8e72b3138</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Annapolis, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e749bf18c9ccc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>MS Fabric</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=6ec086aef45de637</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>SQL AND ETL DEVELOPER</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de66891cd1166601</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-13.xlsx
+++ b/results/job_matches_2026-06-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Databricks SME</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Scicom Infrastructure Services</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive, HBase</t>
+          <t>AWS, S3, IAM, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461cc5e336726e29</t>
+          <t>https://www.indeed.com/viewjob?jk=41d30cbd51be105d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Engineer, Mid</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Acentra Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, Hive</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=041571d1844e3878</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6f9d2703398a29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Cybersecurity Data Engineer - AI/ML SME</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Hive, Spark</t>
+          <t>AWS, EMR, Kinesis, RDS, Spark, Scala, Kafka, Dask, ETL, MLOps</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e6f9d91bf791b1</t>
+          <t>https://www.indeed.com/viewjob?jk=599be78bf8533a28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Databricks SME</t>
+          <t>Experienced AWS Solutions Architect and Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Scicom Infrastructure Services</t>
+          <t>Kaizen Analytix LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d30cbd51be105d</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f364a3ec32fde4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Brookfield Properties</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08447131564025e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb497e82428572d4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer, Mid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Acentra Health</t>
+          <t>WaFd Bank</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6f9d2703398a29</t>
+          <t>https://www.indeed.com/viewjob?jk=c1dd83ec2340a8ca</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data &amp; Software Engineer</t>
+          <t>Senior Python &amp; SAS Developer (Data Modernization)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Illumen Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, Unity Catalog, Spark, PySpark, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8627b9fa5d939b34</t>
+          <t>https://www.indeed.com/viewjob?jk=d892ead602b58795</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Cloud Architect</t>
+          <t>AI/ML Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Intelex</t>
+          <t>QuidelOrtho Corporation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9addd16d08dc466</t>
+          <t>https://www.indeed.com/viewjob?jk=83b31d482e2d3c8b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer - AI/ML SME</t>
+          <t>AI/ML Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>QuidelOrtho Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, RDS, Spark, Scala, Kafka, Dask, ETL, MLOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599be78bf8533a28</t>
+          <t>https://www.indeed.com/viewjob?jk=859e7ca77b35594f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Experienced AWS Solutions Architect and Data Architect</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kaizen Analytix LLC</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Latham, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM, RDS</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f364a3ec32fde4</t>
+          <t>https://www.indeed.com/viewjob?jk=30db4d87acabac99</t>
         </is>
       </c>
     </row>
@@ -823,20 +823,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Brookfield Properties</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb497e82428572d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7edd80e431e58210</t>
         </is>
       </c>
     </row>
@@ -858,55 +858,55 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WaFd Bank</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dd83ec2340a8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=7af97ac7780e4ad6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Python &amp; SAS Developer (Data Modernization)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Illumen Group</t>
+          <t>Midrex Technologies Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d892ead602b58795</t>
+          <t>https://www.indeed.com/viewjob?jk=06f7fe854f6a6907</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DEVOPS ENGINEER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>NYC Human Resources Administration</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, ELT, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6c83582ab47968</t>
+          <t>https://www.indeed.com/viewjob?jk=1766fc067ea2cb5c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer (Databricks)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>QuidelOrtho Corporation</t>
+          <t>uShip</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b31d482e2d3c8b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae560083a24a530c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer (Databricks)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>QuidelOrtho Corporation</t>
+          <t>K&amp;L GATES</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859e7ca77b35594f</t>
+          <t>https://www.indeed.com/viewjob?jk=37aff8f440d6ba6d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Sr. Data Engineer - Ag &amp; Trading</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latham, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db4d87acabac99</t>
+          <t>https://www.indeed.com/viewjob?jk=a8edb3b00b860017</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1077,11 +1077,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7edd80e431e58210</t>
+          <t>https://www.indeed.com/viewjob?jk=6b4b729357fee0da</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7af97ac7780e4ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5860ee0655d6fc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Midrex Technologies Inc</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f7fe854f6a6907</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e67b07fb6f9c29</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DEVOPS ENGINEER</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NYC Human Resources Administration</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, ELT, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1766fc067ea2cb5c</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebd82ca33ca821</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AWS Full Stack Software Engineer</t>
+          <t>Data Engineer, Platform Modernization (Data Warehouse Programmer/Analyst)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hiring Group</t>
+          <t>Caloptima</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc54c80bec441143</t>
+          <t>https://www.indeed.com/viewjob?jk=0dfe4169ae274aad</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Migration Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>uShip</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae560083a24a530c</t>
+          <t>https://www.indeed.com/viewjob?jk=88c5b3637f5dab83</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Power BI</t>
+          <t>AWS, EMR, Redshift, Athena, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37aff8f440d6ba6d</t>
+          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Ag &amp; Trading</t>
+          <t>Forward Deployed Software Engineer (FDE), Advanced</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8edb3b00b860017</t>
+          <t>https://www.indeed.com/viewjob?jk=3cbdae324f66576f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Senior Data Transformation Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Patriot Bank, N.A.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b4b729357fee0da</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee61801e58afe80</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5860ee0655d6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e67b07fb6f9c29</t>
+          <t>https://www.indeed.com/viewjob?jk=9554665f7af0eaf0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Sr Platform Engineer-1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebd82ca33ca821</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer, Platform Modernization (Data Warehouse Programmer/Analyst)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Caloptima</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dfe4169ae274aad</t>
+          <t>https://www.indeed.com/viewjob?jk=4d14a0ff9f2e641c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer, Geospatial Data</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Civitech</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,277 +1546,277 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d28890cbb8b4f4</t>
+          <t>https://www.indeed.com/viewjob?jk=66ed44d25f7a706b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Migration Architect</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c5b3637f5dab83</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0905912913a35c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
+          <t>https://www.indeed.com/viewjob?jk=eb5b987c1cb763e9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure &amp; Microsoft Fabric</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56fe4f99d705b6f4</t>
+          <t>https://www.indeed.com/viewjob?jk=19fa9727f194c93a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>iHeartMedia</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hive, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356a68911d5f594b</t>
+          <t>https://www.indeed.com/viewjob?jk=f89fd566c7357b0a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE), Advanced</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cbdae324f66576f</t>
+          <t>https://www.indeed.com/viewjob?jk=c0be12bfd78e5a42</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
+          <t>https://www.indeed.com/viewjob?jk=fa18885de990da95</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Transformation Data Architect</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Patriot Bank, N.A.</t>
+          <t>GeoLogics Corporation</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee61801e58afe80</t>
+          <t>https://www.indeed.com/viewjob?jk=b66dbbf4e5b40d68</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer-1</t>
+          <t>Bioinformatics Software Engineer II, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Flexential</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=13e882519ae5da00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d14a0ff9f2e641c</t>
+          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,277 +1896,277 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ed44d25f7a706b</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0905912913a35c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb5b987c1cb763e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19fa9727f194c93a</t>
+          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89fd566c7357b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0be12bfd78e5a42</t>
+          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa18885de990da95</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GeoLogics Corporation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66dbbf4e5b40d68</t>
+          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer II, Pathology and Lab Medicine</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e882519ae5da00</t>
+          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
+          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
+          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cain Watters &amp; Associates</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Enterprise Architect, AI Health Cloud</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BrightSpring Health Services</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
+          <t>https://www.indeed.com/viewjob?jk=fafad05a90c901ac</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
+          <t>https://www.indeed.com/viewjob?jk=920269b0f09e721a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
+          <t>https://www.indeed.com/viewjob?jk=3da2910a4a341974</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
+          <t>https://www.indeed.com/viewjob?jk=58b9443c79a19e0d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
+          <t>https://www.indeed.com/viewjob?jk=b88f4a4b03b9105e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec034d4d2c0659b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
+          <t>https://www.indeed.com/viewjob?jk=c012e7a73c63b98f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,602 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Cain Watters &amp; Associates</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Data Engineer - Fabric</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>JSR Tech Consulting</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Enterprise Architect, AI Health Cloud</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>BrightSpring Health Services</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fafad05a90c901ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=920269b0f09e721a</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3da2910a4a341974</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Springfield, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58b9443c79a19e0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b88f4a4b03b9105e</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec034d4d2c0659b</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c012e7a73c63b98f</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Albany, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=8efd67ad513c0fe2</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Trenton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff87cc807f59577</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Providence, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44a0a9b3d5879441</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=874c25ddadc07b4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Little Rock, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf72861040f23682</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91f24b220aab5d6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>MS Fabric</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec086aef45de637</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-13.xlsx
+++ b/results/job_matches_2026-06-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks SME</t>
+          <t>Data Engineer, Mid</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Scicom Infrastructure Services</t>
+          <t>Acentra Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d30cbd51be105d</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6f9d2703398a29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer, Mid</t>
+          <t>Senior Cybersecurity Data Engineer - AI/ML SME</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Acentra Health</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, EMR, Kinesis, RDS, Spark, Scala, Kafka, Dask, ETL, MLOps</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6f9d2703398a29</t>
+          <t>https://www.indeed.com/viewjob?jk=599be78bf8533a28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer - AI/ML SME</t>
+          <t>Experienced AWS Solutions Architect and Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Kaizen Analytix LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, RDS, Spark, Scala, Kafka, Dask, ETL, MLOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599be78bf8533a28</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f364a3ec32fde4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Experienced AWS Solutions Architect and Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kaizen Analytix LLC</t>
+          <t>WaFd Bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM, RDS</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f364a3ec32fde4</t>
+          <t>https://www.indeed.com/viewjob?jk=c1dd83ec2340a8ca</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Brookfield Properties</t>
+          <t>QuidelOrtho Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb497e82428572d4</t>
+          <t>https://www.indeed.com/viewjob?jk=83b31d482e2d3c8b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WaFd Bank</t>
+          <t>QuidelOrtho Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dd83ec2340a8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=859e7ca77b35594f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Python &amp; SAS Developer (Data Modernization)</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Illumen Group</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Latham, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d892ead602b58795</t>
+          <t>https://www.indeed.com/viewjob?jk=30db4d87acabac99</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer (Databricks)</t>
+          <t>DEVOPS ENGINEER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>QuidelOrtho Corporation</t>
+          <t>NYC Human Resources Administration</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, ELT, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b31d482e2d3c8b</t>
+          <t>https://www.indeed.com/viewjob?jk=1766fc067ea2cb5c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer (Databricks)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>QuidelOrtho Corporation</t>
+          <t>Midrex Technologies Inc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859e7ca77b35594f</t>
+          <t>https://www.indeed.com/viewjob?jk=06f7fe854f6a6907</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Sr. Data Engineer - Ag &amp; Trading</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latham, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db4d87acabac99</t>
+          <t>https://www.indeed.com/viewjob?jk=a8edb3b00b860017</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7edd80e431e58210</t>
+          <t>https://www.indeed.com/viewjob?jk=6b4b729357fee0da</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7af97ac7780e4ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5860ee0655d6fc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Midrex Technologies Inc</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f7fe854f6a6907</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e67b07fb6f9c29</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DEVOPS ENGINEER</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NYC Human Resources Administration</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, ELT, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1766fc067ea2cb5c</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebd82ca33ca821</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Migration Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>uShip</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae560083a24a530c</t>
+          <t>https://www.indeed.com/viewjob?jk=88c5b3637f5dab83</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Power BI</t>
+          <t>AWS, EMR, Redshift, Athena, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37aff8f440d6ba6d</t>
+          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Ag &amp; Trading</t>
+          <t>Forward Deployed Software Engineer (FDE), Advanced</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8edb3b00b860017</t>
+          <t>https://www.indeed.com/viewjob?jk=3cbdae324f66576f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b4b729357fee0da</t>
+          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Senior Data Transformation Data Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Patriot Bank, N.A.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5860ee0655d6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee61801e58afe80</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e67b07fb6f9c29</t>
+          <t>https://www.indeed.com/viewjob?jk=9554665f7af0eaf0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Sr Platform Engineer-1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebd82ca33ca821</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer, Platform Modernization (Data Warehouse Programmer/Analyst)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Caloptima</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dfe4169ae274aad</t>
+          <t>https://www.indeed.com/viewjob?jk=4d14a0ff9f2e641c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Migration Architect</t>
+          <t>Bioinformatics Software Engineer II, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,172 +1266,172 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c5b3637f5dab83</t>
+          <t>https://www.indeed.com/viewjob?jk=13e882519ae5da00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0905912913a35c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE), Advanced</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cbdae324f66576f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb5b987c1cb763e9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Transformation Data Architect</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Patriot Bank, N.A.</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee61801e58afe80</t>
+          <t>https://www.indeed.com/viewjob?jk=19fa9727f194c93a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
+          <t>https://www.indeed.com/viewjob?jk=f89fd566c7357b0a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,102 +1441,102 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9554665f7af0eaf0</t>
+          <t>https://www.indeed.com/viewjob?jk=c0be12bfd78e5a42</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer-1</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Flexential</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa18885de990da95</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>GeoLogics Corporation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d14a0ff9f2e641c</t>
+          <t>https://www.indeed.com/viewjob?jk=b66dbbf4e5b40d68</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,277 +1546,277 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ed44d25f7a706b</t>
+          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0905912913a35c</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb5b987c1cb763e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19fa9727f194c93a</t>
+          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89fd566c7357b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0be12bfd78e5a42</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa18885de990da95</t>
+          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GeoLogics Corporation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66dbbf4e5b40d68</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer II, Pathology and Lab Medicine</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e882519ae5da00</t>
+          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
+          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
+          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cain Watters &amp; Associates</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
+          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Enterprise Architect, AI Health Cloud</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BrightSpring Health Services</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,567 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Cain Watters &amp; Associates</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Enterprise Architect, AI Health Cloud</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>BrightSpring Health Services</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=fafad05a90c901ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=920269b0f09e721a</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3da2910a4a341974</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Springfield, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58b9443c79a19e0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b88f4a4b03b9105e</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec034d4d2c0659b</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c012e7a73c63b98f</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Senior Software Architect</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Albany, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8efd67ad513c0fe2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-13.xlsx
+++ b/results/job_matches_2026-06-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,70 +538,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Experienced AWS Solutions Architect and Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kaizen Analytix LLC</t>
+          <t>WaFd Bank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM, RDS</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f364a3ec32fde4</t>
+          <t>https://www.indeed.com/viewjob?jk=c1dd83ec2340a8ca</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WaFd Bank</t>
+          <t>QuidelOrtho Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dd83ec2340a8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=83b31d482e2d3c8b</t>
         </is>
       </c>
     </row>
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b31d482e2d3c8b</t>
+          <t>https://www.indeed.com/viewjob?jk=859e7ca77b35594f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer (Databricks)</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>QuidelOrtho Corporation</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Latham, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859e7ca77b35594f</t>
+          <t>https://www.indeed.com/viewjob?jk=30db4d87acabac99</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>DEVOPS ENGINEER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>NYC Human Resources Administration</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latham, NY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, ELT, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db4d87acabac99</t>
+          <t>https://www.indeed.com/viewjob?jk=1766fc067ea2cb5c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DEVOPS ENGINEER</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NYC Human Resources Administration</t>
+          <t>Midrex Technologies Inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, ELT, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1766fc067ea2cb5c</t>
+          <t>https://www.indeed.com/viewjob?jk=06f7fe854f6a6907</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Data Engineer - Ag &amp; Trading</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Midrex Technologies Inc</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f7fe854f6a6907</t>
+          <t>https://www.indeed.com/viewjob?jk=a8edb3b00b860017</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Ag &amp; Trading</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8edb3b00b860017</t>
+          <t>https://www.indeed.com/viewjob?jk=6b4b729357fee0da</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b4b729357fee0da</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5860ee0655d6fc</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5860ee0655d6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e67b07fb6f9c29</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e67b07fb6f9c29</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebd82ca33ca821</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Senior Migration Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebd82ca33ca821</t>
+          <t>https://www.indeed.com/viewjob?jk=88c5b3637f5dab83</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Migration Architect</t>
+          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, EMR, Redshift, Athena, S3, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88c5b3637f5dab83</t>
+          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
+          <t>Forward Deployed Software Engineer (FDE), Advanced</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
+          <t>https://www.indeed.com/viewjob?jk=3cbdae324f66576f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE), Advanced</t>
+          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cbdae324f66576f</t>
+          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
+          <t>Senior Data Transformation Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Patriot Bank, N.A.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee61801e58afe80</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Transformation Data Architect</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Patriot Bank, N.A.</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee61801e58afe80</t>
+          <t>https://www.indeed.com/viewjob?jk=9554665f7af0eaf0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Sr Platform Engineer-1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Flexential</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9554665f7af0eaf0</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer-1</t>
+          <t>Bioinformatics Software Engineer II, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Flexential</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e7de43eaf74c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=13e882519ae5da00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1217,38 +1217,38 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d14a0ff9f2e641c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0905912913a35c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer II, Pathology and Lab Medicine</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e882519ae5da00</t>
+          <t>https://www.indeed.com/viewjob?jk=eb5b987c1cb763e9</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0905912913a35c</t>
+          <t>https://www.indeed.com/viewjob?jk=19fa9727f194c93a</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb5b987c1cb763e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f89fd566c7357b0a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19fa9727f194c93a</t>
+          <t>https://www.indeed.com/viewjob?jk=c0be12bfd78e5a42</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89fd566c7357b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=fa18885de990da95</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>GeoLogics Corporation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,87 +1431,87 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0be12bfd78e5a42</t>
+          <t>https://www.indeed.com/viewjob?jk=b66dbbf4e5b40d68</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa18885de990da95</t>
+          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GeoLogics Corporation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66dbbf4e5b40d68</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01850979279f2ef</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07ce23f5dbdf19</t>
+          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3c789356f7e994</t>
+          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48cbc8763181388</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer- Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d10bc804849af5b</t>
+          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b28274046d1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701386709cebcaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a37901eceddb0</t>
+          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8565e46d3855261</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ed73484e13493c</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c2dde7ced96f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6ce56a857473e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef8be0e5e3f6ad</t>
+          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - Communications, Media, Entertainment &amp; Games</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e929d104585ce86</t>
+          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Communications, Media, Entertainment &amp; Games</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cain Watters &amp; Associates</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83569333ee939a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Enterprise Architect, AI Health Cloud</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BrightSpring Health Services</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,85 +2061,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Cain Watters &amp; Associates</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Enterprise Architect, AI Health Cloud</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>BrightSpring Health Services</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fafad05a90c901ac</t>
         </is>
